--- a/wwwroot/assets/js/map/map_data/environmental_and_natural_resources/physiography_and_geology/physiographic_units/legend_Color_physiography.xlsx
+++ b/wwwroot/assets/js/map/map_data/environmental_and_natural_resources/physiography_and_geology/physiographic_units/legend_Color_physiography.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\CRS\For RMO\physiography\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\1.THEMEWISE_DATA_HUB\map_data\environmental_and_natural_resources\physiography_and_geology\physiographic_units\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F90048A-1A74-4E54-9F7C-A820A94A7CEA}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58E27776-78A8-4B9C-AC3D-744BC420A1BD}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -885,7 +885,7 @@
           </a:r>
           <a:r>
             <a:rPr lang="en-US" sz="1800" baseline="0"/>
-            <a:t> "lgndIdName' field and display name refers to "Name" field in shapefile</a:t>
+            <a:t> "LegendId' field and display name refers to "Name" field in shapefile</a:t>
           </a:r>
           <a:endParaRPr lang="en-US" sz="1800"/>
         </a:p>
